--- a/data/trans_dic/P32C-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,85</t>
+          <t>0,32; 3,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,23</t>
+          <t>1,09; 5,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,42 +732,42 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,24</t>
+          <t>0,43; 2,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,48</t>
+          <t>0,8; 3,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,46</t>
+          <t>0,43; 5,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,24</t>
+          <t>0,43; 4,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,95</t>
+          <t>0,08; 2,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,41</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,55</t>
+          <t>0,28; 3,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,17</t>
+          <t>0,25; 2,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,66</t>
+          <t>0,05; 1,7</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,32</t>
+          <t>0,59; 3,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,61</t>
+          <t>0,32; 2,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,37</t>
+          <t>0,34; 3,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,19</t>
+          <t>0,32; 2,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,79</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,93</t>
+          <t>0,49; 2,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,23</t>
+          <t>0,23; 2,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,96</t>
+          <t>0,3; 3,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,62</t>
+          <t>0,27; 2,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,15</t>
+          <t>1,57; 4,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,34</t>
+          <t>1,2; 3,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,22</t>
+          <t>0,99; 3,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,46</t>
+          <t>0,55; 2,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,42</t>
+          <t>1,28; 3,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,61</t>
+          <t>0,91; 2,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,58</t>
+          <t>0,88; 2,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,65</t>
+          <t>0,35; 1,68</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,99</t>
+          <t>1,29; 5,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,29</t>
+          <t>1,51; 5,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,77</t>
+          <t>0,96; 4,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,11</t>
+          <t>1,44; 5,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,63</t>
+          <t>0,0; 6,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,06</t>
+          <t>0,41; 3,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,64</t>
+          <t>1,29; 4,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,64</t>
+          <t>1,15; 3,66</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,88</t>
+          <t>0,63; 2,9</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,33</t>
+          <t>1,36; 4,25</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>0,0; 4,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,31</t>
+          <t>0,38; 3,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,41</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,55</t>
+          <t>0,28; 2,38</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,73</t>
+          <t>0,48; 2,89</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,58</t>
+          <t>1,38; 2,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,81</t>
+          <t>1,47; 2,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,26</t>
+          <t>1,04; 2,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,86</t>
+          <t>0,78; 1,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,83</t>
+          <t>0,39; 1,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,78</t>
+          <t>0,1; 0,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,21</t>
+          <t>0,18; 1,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,66</t>
+          <t>0,3; 1,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,11</t>
+          <t>1,16; 2,12</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 1,9</t>
+          <t>1,02; 1,94</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,69</t>
+          <t>0,87; 1,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,55</t>
+          <t>0,69; 1,52</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca</t>
+          <t>Población que ha bebido alguna vez para calmar los nervios o para evitar la resaca (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>928; 8237</t>
+          <t>921; 8991</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3393; 15226</t>
+          <t>3187; 15447</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6197</t>
+          <t>0; 6201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4451</t>
+          <t>0; 4803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5278</t>
+          <t>0; 5961</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2105</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2034</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4291</t>
+          <t>0; 4490</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1626; 9318</t>
+          <t>1782; 10544</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2980; 15241</t>
+          <t>3504; 15352</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6805</t>
+          <t>0; 6717</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>495; 6015</t>
+          <t>493; 6020</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8811</t>
+          <t>0; 8687</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1822; 13842</t>
+          <t>1092; 14380</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1058; 9943</t>
+          <t>1019; 9888</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>161; 6283</t>
+          <t>170; 5687</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5217</t>
+          <t>0; 5353</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2102</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2038</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1230</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9439</t>
+          <t>0; 9780</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1797; 14049</t>
+          <t>1099; 14546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1028; 9156</t>
+          <t>1070; 9619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>164; 5739</t>
+          <t>171; 5873</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1975; 11261</t>
+          <t>1990; 11314</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1074; 10056</t>
+          <t>1232; 9748</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1116; 11011</t>
+          <t>1121; 11505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>699; 6732</t>
+          <t>684; 6032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2040</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5438</t>
+          <t>0; 5737</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 1119</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1934; 11729</t>
+          <t>1947; 10545</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1023; 10313</t>
+          <t>1088; 10992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1130; 11328</t>
+          <t>1135; 13076</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>701; 6594</t>
+          <t>686; 6115</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9864; 27763</t>
+          <t>10535; 28021</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7732; 21943</t>
+          <t>7877; 21910</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6512; 21089</t>
+          <t>6480; 22617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2760; 12537</t>
+          <t>2789; 13473</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7215</t>
+          <t>0; 7278</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4911</t>
+          <t>0; 5526</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6928</t>
+          <t>0; 6430</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6388</t>
+          <t>0; 6950</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11529; 29514</t>
+          <t>11022; 29892</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8300; 23114</t>
+          <t>8069; 23342</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8351; 24609</t>
+          <t>8356; 24090</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2860; 15215</t>
+          <t>3217; 15489</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2788; 12934</t>
+          <t>2779; 12373</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4788; 16076</t>
+          <t>4597; 15999</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3335; 14820</t>
+          <t>2989; 14406</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3415; 14162</t>
+          <t>3329; 13519</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 9309</t>
+          <t>0; 9770</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 7095</t>
+          <t>0; 6135</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1976</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>541; 5323</t>
+          <t>539; 4993</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3960; 16528</t>
+          <t>4595; 17803</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5501; 17756</t>
+          <t>5616; 17881</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3166; 14321</t>
+          <t>3125; 14408</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5179; 15728</t>
+          <t>4944; 15410</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5301</t>
+          <t>0; 5578</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5526</t>
+          <t>0; 6848</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5838</t>
+          <t>0; 5843</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7130</t>
+          <t>0; 6146</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5130</t>
+          <t>0; 5219</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>920; 8209</t>
+          <t>931; 8718</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11422</t>
+          <t>0; 11404</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1009; 9118</t>
+          <t>1006; 8527</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 7498</t>
+          <t>0; 8297</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1921; 11125</t>
+          <t>1953; 11775</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 11196</t>
+          <t>0; 10555</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>24430; 48491</t>
+          <t>25921; 50592</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29486; 57149</t>
+          <t>29887; 54112</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22618; 44619</t>
+          <t>20608; 43642</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12777; 28667</t>
+          <t>12009; 27269</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3529; 16377</t>
+          <t>3470; 17009</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>995; 8131</t>
+          <t>997; 8537</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2905; 13569</t>
+          <t>2058; 12663</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3061; 16709</t>
+          <t>3012; 17382</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>31373; 58458</t>
+          <t>32246; 58847</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31034; 58411</t>
+          <t>31239; 59534</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26733; 52523</t>
+          <t>27060; 53161</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17539; 39431</t>
+          <t>17638; 38596</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32C-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32C-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,11</t>
+          <t>0,31; 2,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 5,3</t>
+          <t>1,21; 5,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 3,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,53</t>
+          <t>0,42; 2,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,5</t>
+          <t>0,68; 3,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,35</t>
+          <t>0,11; 1,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,68</t>
+          <t>0,42; 5,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,22</t>
+          <t>0,45; 4,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,67</t>
+          <t>0,31; 3,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,67</t>
+          <t>0,46; 4,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,28</t>
+          <t>0,26; 2,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,7</t>
+          <t>0,19; 1,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,34</t>
+          <t>0,56; 3,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,53</t>
+          <t>0,29; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,52</t>
+          <t>0,34; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,85</t>
+          <t>0,34; 3,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 11,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,63</t>
+          <t>0,58; 2,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,37</t>
+          <t>0,23; 2,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,42</t>
+          <t>0,3; 3,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,43</t>
+          <t>0,29; 2,37</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 4,19</t>
+          <t>1,49; 4,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,33</t>
+          <t>1,15; 3,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,45</t>
+          <t>1,08; 3,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,64</t>
+          <t>0,57; 2,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,37; 5,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,46</t>
+          <t>1,25; 3,35</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,63</t>
+          <t>0,92; 2,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,53</t>
+          <t>0,88; 2,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,68</t>
+          <t>0,73; 2,54</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -1277,32 +1277,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,73</t>
+          <t>1,32; 6,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,26</t>
+          <t>1,53; 5,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,63</t>
+          <t>1,0; 4,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,83</t>
+          <t>1,38; 5,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,96</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,34 +1312,34 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,81</t>
+          <t>0,45; 3,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,99</t>
+          <t>1,34; 4,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,66</t>
+          <t>1,1; 3,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,9</t>
+          <t>0,63; 3,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,25</t>
+          <t>1,27; 3,85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,0</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,91</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 4,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,52</t>
+          <t>0,37; 3,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 9,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,38</t>
+          <t>0,28; 2,31</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,89</t>
+          <t>0,47; 2,85</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,7</t>
+          <t>1,34; 2,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,66</t>
+          <t>1,46; 2,81</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,21</t>
+          <t>1,1; 2,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,77</t>
+          <t>0,79; 1,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,9</t>
+          <t>0,41; 1,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,82</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,12</t>
+          <t>0,18; 1,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,73</t>
+          <t>0,58; 2,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,12</t>
+          <t>1,11; 2,14</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,94</t>
+          <t>1,06; 1,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,71</t>
+          <t>0,86; 1,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,52</t>
+          <t>0,81; 1,69</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2230</t>
         </is>
       </c>
     </row>
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>921; 8991</t>
+          <t>906; 8572</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3187; 15447</t>
+          <t>3516; 16446</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6201</t>
+          <t>0; 5918</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4803</t>
+          <t>0; 4277</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5961</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1962,27 +1962,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4490</t>
+          <t>0; 4726</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1782; 10544</t>
+          <t>1761; 10541</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3504; 15352</t>
+          <t>2984; 15678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6717</t>
+          <t>0; 6737</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>493; 6020</t>
+          <t>540; 5948</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2565</t>
         </is>
       </c>
     </row>
@@ -2135,27 +2135,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 8687</t>
+          <t>0; 9334</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1092; 14380</t>
+          <t>1062; 13274</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1019; 9888</t>
+          <t>1047; 9455</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>170; 5687</t>
+          <t>701; 6986</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5353</t>
+          <t>0; 5632</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2175,22 +2175,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 9780</t>
+          <t>0; 10424</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1099; 14546</t>
+          <t>1817; 15963</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1070; 9619</t>
+          <t>1115; 10989</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>171; 5873</t>
+          <t>703; 7308</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2467</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1990; 11314</t>
+          <t>1899; 10991</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1232; 9748</t>
+          <t>1116; 10669</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1121; 11505</t>
+          <t>1115; 10438</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>684; 6032</t>
+          <t>773; 6993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5737</t>
+          <t>0; 6116</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2383,22 +2383,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1947; 10545</t>
+          <t>2336; 10979</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1088; 10992</t>
+          <t>1086; 10026</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1135; 13076</t>
+          <t>1129; 12110</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>686; 6115</t>
+          <t>788; 6500</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6416</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8442</t>
+          <t>10851</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10535; 28021</t>
+          <t>10010; 27821</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7877; 21910</t>
+          <t>7581; 22946</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6480; 22617</t>
+          <t>7111; 22328</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2789; 13473</t>
+          <t>3083; 13753</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7278</t>
+          <t>0; 7315</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5526</t>
+          <t>0; 5052</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6430</t>
+          <t>0; 7354</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6950</t>
+          <t>862; 13005</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11022; 29892</t>
+          <t>10788; 28870</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8069; 23342</t>
+          <t>8166; 22990</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8356; 24090</t>
+          <t>8413; 23248</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3217; 15489</t>
+          <t>5618; 19658</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>9473</t>
         </is>
       </c>
     </row>
@@ -2759,32 +2759,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2779; 12373</t>
+          <t>2846; 13627</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4597; 15999</t>
+          <t>4659; 15817</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2989; 14406</t>
+          <t>3119; 14112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3329; 13519</t>
+          <t>3565; 14194</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 9770</t>
+          <t>0; 9635</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6135</t>
+          <t>0; 4444</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2794,34 +2794,34 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>539; 4993</t>
+          <t>691; 5528</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4595; 17803</t>
+          <t>4775; 17506</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5616; 17881</t>
+          <t>5362; 18086</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3125; 14408</t>
+          <t>3137; 15076</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4944; 15410</t>
+          <t>5236; 15820</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2224</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5578</t>
+          <t>0; 5868</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6848</t>
+          <t>0; 5328</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5843</t>
+          <t>0; 6755</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6146</t>
+          <t>0; 7081</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5219</t>
+          <t>0; 5193</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>931; 8718</t>
+          <t>918; 9249</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 11404</t>
+          <t>0; 11629</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1006; 8527</t>
+          <t>1008; 8273</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 8297</t>
+          <t>0; 8392</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1953; 11775</t>
+          <t>1916; 11611</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 10555</t>
+          <t>0; 11279</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>29810</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25921; 50592</t>
+          <t>25226; 48493</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29887; 54112</t>
+          <t>29692; 57119</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20608; 43642</t>
+          <t>21650; 45180</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12009; 27269</t>
+          <t>13056; 29451</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3470; 17009</t>
+          <t>3702; 16168</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>997; 8537</t>
+          <t>0; 8126</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2058; 12663</t>
+          <t>2029; 12945</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3012; 17382</t>
+          <t>5093; 22669</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>32246; 58847</t>
+          <t>30650; 59366</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31239; 59534</t>
+          <t>32459; 59162</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>27060; 53161</t>
+          <t>26821; 52759</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>17638; 38596</t>
+          <t>20344; 42542</t>
         </is>
       </c>
     </row>
